--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.54046987708949</v>
+        <v>12.27532635502704</v>
       </c>
       <c r="D2" t="n">
-        <v>18.10704197641908</v>
+        <v>2.942394321168101</v>
       </c>
       <c r="E2" t="n">
-        <v>17.11209963178889</v>
+        <v>2.780716190165694</v>
       </c>
       <c r="F2" t="n">
-        <v>12.32729112900896</v>
+        <v>2.003184808463956</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.31586748300546</v>
+        <v>11.75132846598839</v>
       </c>
       <c r="D3" t="n">
-        <v>20.81708838280109</v>
+        <v>3.382776862205178</v>
       </c>
       <c r="E3" t="n">
-        <v>17.11209963178889</v>
+        <v>2.780716190165694</v>
       </c>
       <c r="F3" t="n">
-        <v>12.32729112900896</v>
+        <v>2.003184808463956</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.67918112880253</v>
+        <v>11.16036693343041</v>
       </c>
       <c r="D4" t="n">
-        <v>44.86925450684466</v>
+        <v>7.291253857362258</v>
       </c>
       <c r="E4" t="n">
-        <v>17.11209963178889</v>
+        <v>2.780716190165694</v>
       </c>
       <c r="F4" t="n">
-        <v>12.32729112900896</v>
+        <v>2.003184808463956</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.85706620398997</v>
+        <v>5.01427325814837</v>
       </c>
       <c r="D5" t="n">
-        <v>22.78035215804278</v>
+        <v>3.701807225681953</v>
       </c>
       <c r="E5" t="n">
-        <v>17.11209963178889</v>
+        <v>2.780716190165694</v>
       </c>
       <c r="F5" t="n">
-        <v>12.32729112900896</v>
+        <v>2.003184808463956</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.15029989745366</v>
+        <v>6.52442373333622</v>
       </c>
       <c r="D6" t="n">
-        <v>12.69883929322421</v>
+        <v>2.063561385148934</v>
       </c>
       <c r="E6" t="n">
-        <v>17.11209963178889</v>
+        <v>2.780716190165694</v>
       </c>
       <c r="F6" t="n">
-        <v>12.32729112900896</v>
+        <v>2.003184808463956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.94969608046153</v>
+        <v>7.791825613074999</v>
       </c>
       <c r="D7" t="n">
-        <v>42.90049216268807</v>
+        <v>6.971329976436812</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11209963178889</v>
+        <v>2.780716190165694</v>
       </c>
       <c r="F7" t="n">
-        <v>12.32729112900896</v>
+        <v>2.003184808463956</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
